--- a/src/main/java/com/personal/textscrapper/utility/images/output.xlsx
+++ b/src/main/java/com/personal/textscrapper/utility/images/output.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A61FE924-C54B-4C4D-B6CB-5B7969980BDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Extracted Data" sheetId="2" r:id="rId1"/>
@@ -14,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="442">
   <si>
     <t>File no</t>
   </si>
@@ -104,12 +105,1248 @@
   </si>
   <si>
     <t>Remarks</t>
+  </si>
+  <si>
+    <t>1646</t>
+  </si>
+  <si>
+    <t>FormNo</t>
+  </si>
+  <si>
+    <t>Mr.</t>
+  </si>
+  <si>
+    <t>James</t>
+  </si>
+  <si>
+    <t>Yabut</t>
+  </si>
+  <si>
+    <t>MJY</t>
+  </si>
+  <si>
+    <t>james.yabut@cfp-software.co.uk</t>
+  </si>
+  <si>
+    <t>Marni Yabut</t>
+  </si>
+  <si>
+    <t>04/11/1989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Male </t>
+  </si>
+  <si>
+    <t>Service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 More London Riverside </t>
+  </si>
+  <si>
+    <t xml:space="preserve">London, GLN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SE1 2RT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">UK </t>
+  </si>
+  <si>
+    <t xml:space="preserve">O2 </t>
+  </si>
+  <si>
+    <t>Tango - 407317337</t>
+  </si>
+  <si>
+    <t>O218LF+!$!/H5679</t>
+  </si>
+  <si>
+    <t>JHLrmI477351338PS90</t>
+  </si>
+  <si>
+    <t>CDMA+GSM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nokia 6234 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">579381 - 74 - 378533 - 0 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">%|?%%&amp; - ?! -336094-4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TurboCall </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MasterCardGold </t>
+  </si>
+  <si>
+    <t>991</t>
+  </si>
+  <si>
+    <t>14/05/2005</t>
+  </si>
+  <si>
+    <t>14/05/2007</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. </t>
+  </si>
+  <si>
+    <t>Andrea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West </t>
+  </si>
+  <si>
+    <t>MAW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">info@terbell.co.uk </t>
+  </si>
+  <si>
+    <t xml:space="preserve">J. Anthony West </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27/08/1973 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Services </t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 George Street </t>
+  </si>
+  <si>
+    <t xml:space="preserve">London,GLN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">W1U 7GA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vodafone </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Echo - 94057247 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vfone89Ne%*&amp;*%v48 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">UHP1eG106273544IK88 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSM </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nokia 5180iP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">918764 - 39 - 492673 - 1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">%*@$|* - ** - 529620 - 9 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turbo Call </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master Card Silver </t>
+  </si>
+  <si>
+    <t xml:space="preserve">519 </t>
+  </si>
+  <si>
+    <t>10/06/2002</t>
+  </si>
+  <si>
+    <t>10/06/2004</t>
+  </si>
+  <si>
+    <t>Mr</t>
+  </si>
+  <si>
+    <t>Sarah</t>
+  </si>
+  <si>
+    <t>Wright</t>
+  </si>
+  <si>
+    <t>MSW</t>
+  </si>
+  <si>
+    <t>sjwright@ukces.org.uk</t>
+  </si>
+  <si>
+    <t>Jostino Wright</t>
+  </si>
+  <si>
+    <t>15/02/1957</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1F, 78 St James Street </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SW1A 1EJ </t>
+  </si>
+  <si>
+    <t>Orange</t>
+  </si>
+  <si>
+    <t>Echo - 6476456</t>
+  </si>
+  <si>
+    <t>ORN48rQ!@*#&amp;$?d7507</t>
+  </si>
+  <si>
+    <t>VJS1nQ548734156UZ65</t>
+  </si>
+  <si>
+    <t>GSM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T730 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">922091-74-289948-1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">$$*#&amp;#-$*- 487009-9 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master Card Premium Gold </t>
+  </si>
+  <si>
+    <t xml:space="preserve">703 </t>
+  </si>
+  <si>
+    <t>27/08/2002</t>
+  </si>
+  <si>
+    <t>27/02/2004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mrs </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amy </t>
+  </si>
+  <si>
+    <t>Charlesworth</t>
+  </si>
+  <si>
+    <t>MAC</t>
+  </si>
+  <si>
+    <t>amy@christianlifechurch.co.uk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sameh Charlesworth </t>
+  </si>
+  <si>
+    <t xml:space="preserve">18/06/1965 </t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployed </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2Nd Floor Gresham House 53 Clarendon Rd Watford Hertfordshire </t>
+  </si>
+  <si>
+    <t>Watford,GLN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WD17 1LA </t>
+  </si>
+  <si>
+    <t>UK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-Mobile </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gama-51016138 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-M27xS:#&amp;/$&amp;k5429 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VFBjsI901137269LZ68 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siemens CF75 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">690468 - 52-702689-8 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">#$!#?&amp; - %# - 704001 - 6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Economy Plus </t>
+  </si>
+  <si>
+    <t>Master Card Premium Gold</t>
+  </si>
+  <si>
+    <t>972</t>
+  </si>
+  <si>
+    <t>16/06/2005</t>
+  </si>
+  <si>
+    <t>16/02/2008</t>
+  </si>
+  <si>
+    <t>1647</t>
+  </si>
+  <si>
+    <t>Luke</t>
+  </si>
+  <si>
+    <t>Menzies</t>
+  </si>
+  <si>
+    <t>MLM</t>
+  </si>
+  <si>
+    <t>treasurer.menzies@carlsonmarketing.com</t>
+  </si>
+  <si>
+    <t>Nauman Menzies</t>
+  </si>
+  <si>
+    <t>11/01/1964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Professional </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pilot Way, Ansty Business Park </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coventry, WAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CV7 9JU </t>
+  </si>
+  <si>
+    <t>Gama - 622056447</t>
+  </si>
+  <si>
+    <t>Vfone67kZ&amp;&amp;+:@Z75</t>
+  </si>
+  <si>
+    <t>SEXcbT714079798VY79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nokia 6260 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">198384 - 72 - 338089 - 4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">$%&amp;+## - #@ - 319747 -5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ultimate </t>
+  </si>
+  <si>
+    <t>Master Card PremiumGold</t>
+  </si>
+  <si>
+    <t>916</t>
+  </si>
+  <si>
+    <t>19/12/2005</t>
+  </si>
+  <si>
+    <t>19/06/2007</t>
+  </si>
+  <si>
+    <t>Mrs.</t>
+  </si>
+  <si>
+    <t>Mary</t>
+  </si>
+  <si>
+    <t>Gleeson</t>
+  </si>
+  <si>
+    <t>MMG</t>
+  </si>
+  <si>
+    <t>mgleeson@schlosshotel-kronberg.de</t>
+  </si>
+  <si>
+    <t>Lucy Gleeson</t>
+  </si>
+  <si>
+    <t>03/04/1974</t>
+  </si>
+  <si>
+    <t>Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3A Belwell Lane Sutton </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coldfield, Warwickshire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B74 4AA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virgin </t>
+  </si>
+  <si>
+    <t>Charlie - 76476390</t>
+  </si>
+  <si>
+    <t>Vir20oB%+!@$@o15</t>
+  </si>
+  <si>
+    <t>HXDvtM396609663RW68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nokia6730 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">102681-01- 325592-8 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">!%|@&amp;! - +! - 877222 - 5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A lacarte Pack </t>
+  </si>
+  <si>
+    <t>823</t>
+  </si>
+  <si>
+    <t>23/11/2005</t>
+  </si>
+  <si>
+    <t>23/07/2008</t>
+  </si>
+  <si>
+    <t>MISS</t>
+  </si>
+  <si>
+    <t>Toby</t>
+  </si>
+  <si>
+    <t>Moncaster</t>
+  </si>
+  <si>
+    <t>MTM</t>
+  </si>
+  <si>
+    <t>toby.moncaster@patientline.co.uk</t>
+  </si>
+  <si>
+    <t>Maryanne Moncaster</t>
+  </si>
+  <si>
+    <t>18/10/1969</t>
+  </si>
+  <si>
+    <t>Professional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brinklow Road Binley </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coventry, Warwickshire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CV3 2AB </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha - 9422027 </t>
+  </si>
+  <si>
+    <t>Vfone83fz%@/+&amp;a66</t>
+  </si>
+  <si>
+    <t>KIAhfT330196393MC68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nokia 7370 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">429611 - 10 - 576418 - 3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">!+&amp;%!? - &amp;| - 261653 - 3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PREMIUMPLUS </t>
+  </si>
+  <si>
+    <t>MasterTitanium Plus</t>
+  </si>
+  <si>
+    <t>774</t>
+  </si>
+  <si>
+    <t>24/11/2004</t>
+  </si>
+  <si>
+    <t>24/11/2005</t>
+  </si>
+  <si>
+    <t>Richard</t>
+  </si>
+  <si>
+    <t>Batley</t>
+  </si>
+  <si>
+    <t>MRB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">r.p.batley@coasolutions.com </t>
+  </si>
+  <si>
+    <t>Beto Batley</t>
+  </si>
+  <si>
+    <t>05/04/1986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UnEmployed </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banbury Road Ettington Stratford-upon-Avon, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warwickshire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CV37 7NZ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">England </t>
+  </si>
+  <si>
+    <t>Charlie - 1932904</t>
+  </si>
+  <si>
+    <t>ORNS57fz%|\&amp;#&amp;*n32912</t>
+  </si>
+  <si>
+    <t>PZHwmP371785043BL85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nokia 3152 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">171592 - 96 - 683476 -8 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">$$|@@* - !? - 516297 - 0 </t>
+  </si>
+  <si>
+    <t>Maestro - Platinum</t>
+  </si>
+  <si>
+    <t>604</t>
+  </si>
+  <si>
+    <t>26/12/2003</t>
+  </si>
+  <si>
+    <t>26/12/2006</t>
+  </si>
+  <si>
+    <t>1648</t>
+  </si>
+  <si>
+    <t>Seema</t>
+  </si>
+  <si>
+    <t>Quraishi</t>
+  </si>
+  <si>
+    <t>MSQ</t>
+  </si>
+  <si>
+    <t>seema.quraishi@hilton.com</t>
+  </si>
+  <si>
+    <t>Toufik Quraishi</t>
+  </si>
+  <si>
+    <t>13/01/1973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">l55 Windsor RdW. Glamorgan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neath, WAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAl1 1NU </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hutchison Whampoa </t>
+  </si>
+  <si>
+    <t>Charlie - 46436972</t>
+  </si>
+  <si>
+    <t>HuWh02Qk?!!/:s24208608</t>
+  </si>
+  <si>
+    <t>HDBptM641249814XF77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nokia 2120/2120 plus </t>
+  </si>
+  <si>
+    <t xml:space="preserve">499343 - 70 - 520958 - 4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">!|++$! - $+ - 311685 - 7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classic SMS+ </t>
+  </si>
+  <si>
+    <t>779</t>
+  </si>
+  <si>
+    <t>06/04/2005</t>
+  </si>
+  <si>
+    <t>06/04/2006</t>
+  </si>
+  <si>
+    <t>Mrs</t>
+  </si>
+  <si>
+    <t>Bev</t>
+  </si>
+  <si>
+    <t>MBW</t>
+  </si>
+  <si>
+    <t>bev.wright@cinven.com</t>
+  </si>
+  <si>
+    <t>Ayantha Wright</t>
+  </si>
+  <si>
+    <t>03/04/1986</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c/o The Secretariat, The Information Services Directorate, 40-41 Park Place </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cardiff, WAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CF10 3BB </t>
+  </si>
+  <si>
+    <t>Delta - 628435064</t>
+  </si>
+  <si>
+    <t>Vfone92Zm|$!@/G29</t>
+  </si>
+  <si>
+    <t>XFHwifO128262878BF73</t>
+  </si>
+  <si>
+    <t>CDMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nokia 5320 XpressMusic </t>
+  </si>
+  <si>
+    <t xml:space="preserve">403936 - 47 - 337287 -3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">#!+$?# - $? - 610036 - 8 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALL PLUS </t>
+  </si>
+  <si>
+    <t>MasterCard Premium Gold</t>
+  </si>
+  <si>
+    <t>631</t>
+  </si>
+  <si>
+    <t>16/02/2004</t>
+  </si>
+  <si>
+    <t>16/02/2006</t>
+  </si>
+  <si>
+    <t>Nina</t>
+  </si>
+  <si>
+    <t>Francis</t>
+  </si>
+  <si>
+    <t>MNF</t>
+  </si>
+  <si>
+    <t>nfrancis@tbaplc.co.uk</t>
+  </si>
+  <si>
+    <t>Cam Francis</t>
+  </si>
+  <si>
+    <t>26/08/1989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed income </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colmore Circus, Queensway </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Birmingham, WAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B4 6AR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gama - 6257643 </t>
+  </si>
+  <si>
+    <t>O2311K!@&amp;|!&amp;i416</t>
+  </si>
+  <si>
+    <t>LEQmgG620531205TS87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nokia 7100 Supernova </t>
+  </si>
+  <si>
+    <t xml:space="preserve">019393 - 95 - 323433 - 6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">@$%||$ - !! - 800388 - 2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MasterTitanium Plus </t>
+  </si>
+  <si>
+    <t xml:space="preserve">349 </t>
+  </si>
+  <si>
+    <t>26/04/2003</t>
+  </si>
+  <si>
+    <t>26/04/2004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sylvia </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrows </t>
+  </si>
+  <si>
+    <t>MSB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slyvia.barrows@ccn.ac.uk </t>
+  </si>
+  <si>
+    <t>Liang Barrows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17/01/1958 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pixed income </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warwick Road Stratford-upon-Avon, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CV37 0PY </t>
+  </si>
+  <si>
+    <t xml:space="preserve">UK _ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bravo - 16961237 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vir33Ki/*?/!M112 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MREhoE542849916QH68 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nokia 5120 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">090353 - 39 - 112922 - 7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">+&amp;&amp;?!! - *# - 312796 - 5 </t>
+  </si>
+  <si>
+    <t>Master Card Gold</t>
+  </si>
+  <si>
+    <t>948</t>
+  </si>
+  <si>
+    <t>06/02/2003</t>
+  </si>
+  <si>
+    <t>06/08/2004</t>
+  </si>
+  <si>
+    <t>1649</t>
+  </si>
+  <si>
+    <t>Alastair</t>
+  </si>
+  <si>
+    <t>Eadie</t>
+  </si>
+  <si>
+    <t>MAE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alastair.eadie@ltcas.org.uk </t>
+  </si>
+  <si>
+    <t>Natasha Eadie</t>
+  </si>
+  <si>
+    <t>27/09/1969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed Income </t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 Clarendon Road </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Watford, Hertfordshire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">WD17 1JY </t>
+  </si>
+  <si>
+    <t>Gama - 079476642</t>
+  </si>
+  <si>
+    <t>ORN37Ta:$$!?O288746</t>
+  </si>
+  <si>
+    <t>NHRbiB374412800RE89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siemens A70 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">285781 - 20 - 719783 -6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">%|%#!?- &amp;$ -816290 - 8 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMS Value ++ </t>
+  </si>
+  <si>
+    <t>Visa Titantum-Plus</t>
+  </si>
+  <si>
+    <t>415</t>
+  </si>
+  <si>
+    <t>25/03/2006</t>
+  </si>
+  <si>
+    <t>25/11/2008</t>
+  </si>
+  <si>
+    <t>Rangan</t>
+  </si>
+  <si>
+    <t>Momen</t>
+  </si>
+  <si>
+    <t>MRM</t>
+  </si>
+  <si>
+    <t>rangan.momen@adstream.com</t>
+  </si>
+  <si>
+    <t>Francis Momen</t>
+  </si>
+  <si>
+    <t>17/04/1963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pennyroyal Court, Station Road </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tring, Hertfordshire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HP23 5QY </t>
+  </si>
+  <si>
+    <t>Charlie - 322271258</t>
+  </si>
+  <si>
+    <t>HuWh29mj:|#&amp;;@c9520110</t>
+  </si>
+  <si>
+    <t>XYSppB991608836YW83</t>
+  </si>
+  <si>
+    <t>CDMA+CDMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nokia 2168 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">033378 - 45 - 956701 - 0 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">*!*+&amp;% - %&amp; - 010775 - 7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ultra Plus </t>
+  </si>
+  <si>
+    <t>MasterTitanmum Plus</t>
+  </si>
+  <si>
+    <t>480</t>
+  </si>
+  <si>
+    <t>16/11/2002</t>
+  </si>
+  <si>
+    <t>16/11/2003</t>
+  </si>
+  <si>
+    <t>Michelle</t>
+  </si>
+  <si>
+    <t>Varney</t>
+  </si>
+  <si>
+    <t>MMV</t>
+  </si>
+  <si>
+    <t>michelle@jpmorgan.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kenji Varmey </t>
+  </si>
+  <si>
+    <t>11/08/1972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High Street </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inverness, Highland </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IV2 7QB </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scotland </t>
+  </si>
+  <si>
+    <t>Gama - 1041275</t>
+  </si>
+  <si>
+    <t>HuWh08Tj!:$;:W06708459</t>
+  </si>
+  <si>
+    <t>HEWwxB957296749JW77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nokia 6086 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">430434 - 19 - 645171 - 8 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;&amp;%#!$ - ?# - 889615 - 2 </t>
+  </si>
+  <si>
+    <t>MasterCard PremiumGold</t>
+  </si>
+  <si>
+    <t>698</t>
+  </si>
+  <si>
+    <t>26/09/2003</t>
+  </si>
+  <si>
+    <t>26/09/2004</t>
+  </si>
+  <si>
+    <t>Jean</t>
+  </si>
+  <si>
+    <t>Tuck</t>
+  </si>
+  <si>
+    <t>MJT</t>
+  </si>
+  <si>
+    <t>mcf@relationshipsireland.com</t>
+  </si>
+  <si>
+    <t>Bel Tuck</t>
+  </si>
+  <si>
+    <t>05/06/1950</t>
+  </si>
+  <si>
+    <t>UnEmployed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Six Hills Way, Michael Faraday House </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stevenage, HRT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SG1 2AY </t>
+  </si>
+  <si>
+    <t>Alpha - 445555212</t>
+  </si>
+  <si>
+    <t>HuWh99Ak;@/#&amp;|S9281911</t>
+  </si>
+  <si>
+    <t>VQXwiS653364017LU68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nokia 3587i </t>
+  </si>
+  <si>
+    <t xml:space="preserve">604288 - 80 -828910 - 4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">*#||@* - !+ - 303220 - 9 </t>
+  </si>
+  <si>
+    <t>883</t>
+  </si>
+  <si>
+    <t>07/09/2004</t>
+  </si>
+  <si>
+    <t>07/09/2007</t>
+  </si>
+  <si>
+    <t>1650</t>
+  </si>
+  <si>
+    <t>Miss</t>
+  </si>
+  <si>
+    <t>Peter</t>
+  </si>
+  <si>
+    <t>King</t>
+  </si>
+  <si>
+    <t>MPK</t>
+  </si>
+  <si>
+    <t>press@claire-house.org.uk</t>
+  </si>
+  <si>
+    <t>Dimas King</t>
+  </si>
+  <si>
+    <t>05/02/1989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88 Leadenhall Street, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">London </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EC3A 3BP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foxtrot - 4444748 </t>
+  </si>
+  <si>
+    <t>HuWh71KQ#&amp;%$;@E5975036</t>
+  </si>
+  <si>
+    <t>PKArqU436074560CQ72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siemens M30 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">143940 - 29 - 154363 - 6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">%!*%*$ - %? - 048571 - 7 </t>
+  </si>
+  <si>
+    <t>MasterCard Silver</t>
+  </si>
+  <si>
+    <t>664</t>
+  </si>
+  <si>
+    <t>08/07/2005</t>
+  </si>
+  <si>
+    <t>08/07/2007</t>
+  </si>
+  <si>
+    <t>Britta</t>
+  </si>
+  <si>
+    <t>Burreau</t>
+  </si>
+  <si>
+    <t>MBB</t>
+  </si>
+  <si>
+    <t>britta.burreau@aviatorfarmborough.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hasmukh Burreau </t>
+  </si>
+  <si>
+    <t>03/12/1979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AJB International Centre, IFSC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dublin </t>
+  </si>
+  <si>
+    <t>IE0022</t>
+  </si>
+  <si>
+    <t>Bravo - 27171104</t>
+  </si>
+  <si>
+    <t>O297jO+|!!/L7976</t>
+  </si>
+  <si>
+    <t>XWIihW627753416HN89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ericsson T66 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">169888 - 50 - 153317-5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">%+?#!? - &amp;$ - 450860 - 2 </t>
+  </si>
+  <si>
+    <t>MasterTitanum Plus</t>
+  </si>
+  <si>
+    <t>720</t>
+  </si>
+  <si>
+    <t>07/03/2006</t>
+  </si>
+  <si>
+    <t>Anna</t>
+  </si>
+  <si>
+    <t>Burgin</t>
+  </si>
+  <si>
+    <t>MAB</t>
+  </si>
+  <si>
+    <t>anna.burgin@hotmail.co.uk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kentaro Burgin </t>
+  </si>
+  <si>
+    <t>06/06/1991</t>
+  </si>
+  <si>
+    <t>Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65 Kingsway </t>
+  </si>
+  <si>
+    <t xml:space="preserve">WC2B 6TD </t>
+  </si>
+  <si>
+    <t>Echo - 02131821</t>
+  </si>
+  <si>
+    <t>O248Eh#&amp;*|!;c180</t>
+  </si>
+  <si>
+    <t>ZSKiwN928340307RR68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">i35s </t>
+  </si>
+  <si>
+    <t xml:space="preserve">346613 - 10 - 401783-1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">$?$!# - &amp;$ - 803757 - 0 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMS Pro </t>
+  </si>
+  <si>
+    <t>575</t>
+  </si>
+  <si>
+    <t>04/09/2006</t>
+  </si>
+  <si>
+    <t>04/03/2008</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -190,9 +1427,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -230,9 +1467,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -267,7 +1504,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -302,7 +1539,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -475,16 +1712,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AE20"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="11.6640625" customWidth="1"/>
+    <col min="2" max="2" width="11.6328125" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="27" max="27" width="11.109375" customWidth="1"/>
+    <col min="27" max="27" width="11.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -577,6 +1814,1643 @@
       </c>
       <c r="AE1" s="1" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R2" t="s">
+        <v>47</v>
+      </c>
+      <c r="S2" t="s">
+        <v>48</v>
+      </c>
+      <c r="T2" t="s">
+        <v>49</v>
+      </c>
+      <c r="U2" t="s">
+        <v>50</v>
+      </c>
+      <c r="V2" t="s">
+        <v>51</v>
+      </c>
+      <c r="W2" t="s">
+        <v>52</v>
+      </c>
+      <c r="X2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H3" t="s">
+        <v>64</v>
+      </c>
+      <c r="I3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K3" t="s">
+        <v>66</v>
+      </c>
+      <c r="L3" t="s">
+        <v>67</v>
+      </c>
+      <c r="M3" t="s">
+        <v>68</v>
+      </c>
+      <c r="N3" t="s">
+        <v>69</v>
+      </c>
+      <c r="O3" t="s">
+        <v>44</v>
+      </c>
+      <c r="P3" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R3" t="s">
+        <v>72</v>
+      </c>
+      <c r="S3" t="s">
+        <v>73</v>
+      </c>
+      <c r="T3" t="s">
+        <v>74</v>
+      </c>
+      <c r="U3" t="s">
+        <v>75</v>
+      </c>
+      <c r="V3" t="s">
+        <v>76</v>
+      </c>
+      <c r="W3" t="s">
+        <v>77</v>
+      </c>
+      <c r="X3" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H4" t="s">
+        <v>88</v>
+      </c>
+      <c r="I4" t="s">
+        <v>89</v>
+      </c>
+      <c r="J4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K4" t="s">
+        <v>66</v>
+      </c>
+      <c r="L4" t="s">
+        <v>91</v>
+      </c>
+      <c r="M4" t="s">
+        <v>42</v>
+      </c>
+      <c r="N4" t="s">
+        <v>92</v>
+      </c>
+      <c r="O4" t="s">
+        <v>44</v>
+      </c>
+      <c r="P4" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>94</v>
+      </c>
+      <c r="R4" t="s">
+        <v>95</v>
+      </c>
+      <c r="S4" t="s">
+        <v>96</v>
+      </c>
+      <c r="T4" t="s">
+        <v>97</v>
+      </c>
+      <c r="U4" t="s">
+        <v>98</v>
+      </c>
+      <c r="V4" t="s">
+        <v>99</v>
+      </c>
+      <c r="W4" t="s">
+        <v>100</v>
+      </c>
+      <c r="X4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>103</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E5" t="s">
+        <v>107</v>
+      </c>
+      <c r="F5" t="s">
+        <v>108</v>
+      </c>
+      <c r="G5" t="s">
+        <v>109</v>
+      </c>
+      <c r="H5" t="s">
+        <v>110</v>
+      </c>
+      <c r="I5" t="s">
+        <v>111</v>
+      </c>
+      <c r="J5" t="s">
+        <v>112</v>
+      </c>
+      <c r="K5" t="s">
+        <v>113</v>
+      </c>
+      <c r="L5" t="s">
+        <v>114</v>
+      </c>
+      <c r="M5" t="s">
+        <v>115</v>
+      </c>
+      <c r="N5" t="s">
+        <v>116</v>
+      </c>
+      <c r="O5" t="s">
+        <v>117</v>
+      </c>
+      <c r="P5" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>119</v>
+      </c>
+      <c r="R5" t="s">
+        <v>120</v>
+      </c>
+      <c r="S5" t="s">
+        <v>121</v>
+      </c>
+      <c r="T5" t="s">
+        <v>74</v>
+      </c>
+      <c r="U5" t="s">
+        <v>122</v>
+      </c>
+      <c r="V5" t="s">
+        <v>123</v>
+      </c>
+      <c r="W5" t="s">
+        <v>124</v>
+      </c>
+      <c r="X5" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>131</v>
+      </c>
+      <c r="E6" t="s">
+        <v>132</v>
+      </c>
+      <c r="F6" t="s">
+        <v>133</v>
+      </c>
+      <c r="G6" t="s">
+        <v>134</v>
+      </c>
+      <c r="H6" t="s">
+        <v>135</v>
+      </c>
+      <c r="I6" t="s">
+        <v>136</v>
+      </c>
+      <c r="J6" t="s">
+        <v>90</v>
+      </c>
+      <c r="K6" t="s">
+        <v>137</v>
+      </c>
+      <c r="L6" t="s">
+        <v>138</v>
+      </c>
+      <c r="M6" t="s">
+        <v>139</v>
+      </c>
+      <c r="N6" t="s">
+        <v>140</v>
+      </c>
+      <c r="O6" t="s">
+        <v>44</v>
+      </c>
+      <c r="P6" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>141</v>
+      </c>
+      <c r="R6" t="s">
+        <v>142</v>
+      </c>
+      <c r="S6" t="s">
+        <v>143</v>
+      </c>
+      <c r="T6" t="s">
+        <v>49</v>
+      </c>
+      <c r="U6" t="s">
+        <v>144</v>
+      </c>
+      <c r="V6" t="s">
+        <v>145</v>
+      </c>
+      <c r="W6" t="s">
+        <v>146</v>
+      </c>
+      <c r="X6" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>148</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>149</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>150</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D7" t="s">
+        <v>153</v>
+      </c>
+      <c r="E7" t="s">
+        <v>154</v>
+      </c>
+      <c r="F7" t="s">
+        <v>155</v>
+      </c>
+      <c r="G7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H7" t="s">
+        <v>157</v>
+      </c>
+      <c r="I7" t="s">
+        <v>158</v>
+      </c>
+      <c r="J7" t="s">
+        <v>112</v>
+      </c>
+      <c r="K7" t="s">
+        <v>159</v>
+      </c>
+      <c r="L7" t="s">
+        <v>160</v>
+      </c>
+      <c r="M7" t="s">
+        <v>161</v>
+      </c>
+      <c r="N7" t="s">
+        <v>162</v>
+      </c>
+      <c r="O7" t="s">
+        <v>44</v>
+      </c>
+      <c r="P7" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>164</v>
+      </c>
+      <c r="R7" t="s">
+        <v>165</v>
+      </c>
+      <c r="S7" t="s">
+        <v>166</v>
+      </c>
+      <c r="T7" t="s">
+        <v>97</v>
+      </c>
+      <c r="U7" t="s">
+        <v>167</v>
+      </c>
+      <c r="V7" t="s">
+        <v>168</v>
+      </c>
+      <c r="W7" t="s">
+        <v>169</v>
+      </c>
+      <c r="X7" t="s">
+        <v>170</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>171</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>172</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>174</v>
+      </c>
+      <c r="D8" t="s">
+        <v>175</v>
+      </c>
+      <c r="E8" t="s">
+        <v>176</v>
+      </c>
+      <c r="F8" t="s">
+        <v>177</v>
+      </c>
+      <c r="G8" t="s">
+        <v>178</v>
+      </c>
+      <c r="H8" t="s">
+        <v>179</v>
+      </c>
+      <c r="I8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K8" t="s">
+        <v>181</v>
+      </c>
+      <c r="L8" t="s">
+        <v>182</v>
+      </c>
+      <c r="M8" t="s">
+        <v>183</v>
+      </c>
+      <c r="N8" t="s">
+        <v>184</v>
+      </c>
+      <c r="O8" t="s">
+        <v>44</v>
+      </c>
+      <c r="P8" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>185</v>
+      </c>
+      <c r="R8" t="s">
+        <v>186</v>
+      </c>
+      <c r="S8" t="s">
+        <v>187</v>
+      </c>
+      <c r="T8" t="s">
+        <v>49</v>
+      </c>
+      <c r="U8" t="s">
+        <v>188</v>
+      </c>
+      <c r="V8" t="s">
+        <v>189</v>
+      </c>
+      <c r="W8" t="s">
+        <v>190</v>
+      </c>
+      <c r="X8" t="s">
+        <v>191</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>192</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>194</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" t="s">
+        <v>196</v>
+      </c>
+      <c r="E9" t="s">
+        <v>197</v>
+      </c>
+      <c r="F9" t="s">
+        <v>198</v>
+      </c>
+      <c r="G9" t="s">
+        <v>199</v>
+      </c>
+      <c r="H9" t="s">
+        <v>200</v>
+      </c>
+      <c r="I9" t="s">
+        <v>201</v>
+      </c>
+      <c r="J9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K9" t="s">
+        <v>202</v>
+      </c>
+      <c r="L9" t="s">
+        <v>203</v>
+      </c>
+      <c r="M9" t="s">
+        <v>204</v>
+      </c>
+      <c r="N9" t="s">
+        <v>205</v>
+      </c>
+      <c r="O9" t="s">
+        <v>206</v>
+      </c>
+      <c r="P9" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>207</v>
+      </c>
+      <c r="R9" t="s">
+        <v>208</v>
+      </c>
+      <c r="S9" t="s">
+        <v>209</v>
+      </c>
+      <c r="T9" t="s">
+        <v>97</v>
+      </c>
+      <c r="U9" t="s">
+        <v>210</v>
+      </c>
+      <c r="V9" t="s">
+        <v>211</v>
+      </c>
+      <c r="W9" t="s">
+        <v>212</v>
+      </c>
+      <c r="X9" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>213</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>217</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>218</v>
+      </c>
+      <c r="E10" t="s">
+        <v>219</v>
+      </c>
+      <c r="F10" t="s">
+        <v>220</v>
+      </c>
+      <c r="G10" t="s">
+        <v>221</v>
+      </c>
+      <c r="H10" t="s">
+        <v>222</v>
+      </c>
+      <c r="I10" t="s">
+        <v>223</v>
+      </c>
+      <c r="J10" t="s">
+        <v>90</v>
+      </c>
+      <c r="K10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L10" t="s">
+        <v>224</v>
+      </c>
+      <c r="M10" t="s">
+        <v>225</v>
+      </c>
+      <c r="N10" t="s">
+        <v>226</v>
+      </c>
+      <c r="O10" t="s">
+        <v>44</v>
+      </c>
+      <c r="P10" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>228</v>
+      </c>
+      <c r="R10" t="s">
+        <v>229</v>
+      </c>
+      <c r="S10" t="s">
+        <v>230</v>
+      </c>
+      <c r="T10" t="s">
+        <v>97</v>
+      </c>
+      <c r="U10" t="s">
+        <v>231</v>
+      </c>
+      <c r="V10" t="s">
+        <v>232</v>
+      </c>
+      <c r="W10" t="s">
+        <v>233</v>
+      </c>
+      <c r="X10" t="s">
+        <v>234</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>192</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>235</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>236</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>217</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>238</v>
+      </c>
+      <c r="D11" t="s">
+        <v>239</v>
+      </c>
+      <c r="E11" t="s">
+        <v>85</v>
+      </c>
+      <c r="F11" t="s">
+        <v>240</v>
+      </c>
+      <c r="G11" t="s">
+        <v>241</v>
+      </c>
+      <c r="H11" t="s">
+        <v>242</v>
+      </c>
+      <c r="I11" t="s">
+        <v>243</v>
+      </c>
+      <c r="J11" t="s">
+        <v>112</v>
+      </c>
+      <c r="K11" t="s">
+        <v>244</v>
+      </c>
+      <c r="L11" t="s">
+        <v>245</v>
+      </c>
+      <c r="M11" t="s">
+        <v>246</v>
+      </c>
+      <c r="N11" t="s">
+        <v>247</v>
+      </c>
+      <c r="O11" t="s">
+        <v>117</v>
+      </c>
+      <c r="P11" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>248</v>
+      </c>
+      <c r="R11" t="s">
+        <v>249</v>
+      </c>
+      <c r="S11" t="s">
+        <v>250</v>
+      </c>
+      <c r="T11" t="s">
+        <v>251</v>
+      </c>
+      <c r="U11" t="s">
+        <v>252</v>
+      </c>
+      <c r="V11" t="s">
+        <v>253</v>
+      </c>
+      <c r="W11" t="s">
+        <v>254</v>
+      </c>
+      <c r="X11" t="s">
+        <v>255</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>256</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>257</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>258</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>217</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" t="s">
+        <v>260</v>
+      </c>
+      <c r="E12" t="s">
+        <v>261</v>
+      </c>
+      <c r="F12" t="s">
+        <v>262</v>
+      </c>
+      <c r="G12" t="s">
+        <v>263</v>
+      </c>
+      <c r="H12" t="s">
+        <v>264</v>
+      </c>
+      <c r="I12" t="s">
+        <v>265</v>
+      </c>
+      <c r="J12" t="s">
+        <v>90</v>
+      </c>
+      <c r="K12" t="s">
+        <v>266</v>
+      </c>
+      <c r="L12" t="s">
+        <v>267</v>
+      </c>
+      <c r="M12" t="s">
+        <v>268</v>
+      </c>
+      <c r="N12" t="s">
+        <v>269</v>
+      </c>
+      <c r="O12" t="s">
+        <v>44</v>
+      </c>
+      <c r="P12" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>271</v>
+      </c>
+      <c r="R12" t="s">
+        <v>272</v>
+      </c>
+      <c r="S12" t="s">
+        <v>273</v>
+      </c>
+      <c r="T12" t="s">
+        <v>49</v>
+      </c>
+      <c r="U12" t="s">
+        <v>274</v>
+      </c>
+      <c r="V12" t="s">
+        <v>275</v>
+      </c>
+      <c r="W12" t="s">
+        <v>276</v>
+      </c>
+      <c r="X12" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>277</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>278</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>279</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>217</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>105</v>
+      </c>
+      <c r="D13" t="s">
+        <v>281</v>
+      </c>
+      <c r="E13" t="s">
+        <v>282</v>
+      </c>
+      <c r="F13" t="s">
+        <v>283</v>
+      </c>
+      <c r="G13" t="s">
+        <v>284</v>
+      </c>
+      <c r="H13" t="s">
+        <v>285</v>
+      </c>
+      <c r="I13" t="s">
+        <v>286</v>
+      </c>
+      <c r="J13" t="s">
+        <v>112</v>
+      </c>
+      <c r="K13" t="s">
+        <v>287</v>
+      </c>
+      <c r="L13" t="s">
+        <v>288</v>
+      </c>
+      <c r="M13" t="s">
+        <v>289</v>
+      </c>
+      <c r="N13" t="s">
+        <v>290</v>
+      </c>
+      <c r="O13" t="s">
+        <v>291</v>
+      </c>
+      <c r="P13" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>292</v>
+      </c>
+      <c r="R13" t="s">
+        <v>293</v>
+      </c>
+      <c r="S13" t="s">
+        <v>294</v>
+      </c>
+      <c r="T13" t="s">
+        <v>74</v>
+      </c>
+      <c r="U13" t="s">
+        <v>295</v>
+      </c>
+      <c r="V13" t="s">
+        <v>296</v>
+      </c>
+      <c r="W13" t="s">
+        <v>297</v>
+      </c>
+      <c r="X13" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>298</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>300</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>302</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" t="s">
+        <v>303</v>
+      </c>
+      <c r="E14" t="s">
+        <v>304</v>
+      </c>
+      <c r="F14" t="s">
+        <v>305</v>
+      </c>
+      <c r="G14" t="s">
+        <v>306</v>
+      </c>
+      <c r="H14" t="s">
+        <v>307</v>
+      </c>
+      <c r="I14" t="s">
+        <v>308</v>
+      </c>
+      <c r="J14" t="s">
+        <v>39</v>
+      </c>
+      <c r="K14" t="s">
+        <v>309</v>
+      </c>
+      <c r="L14" t="s">
+        <v>310</v>
+      </c>
+      <c r="M14" t="s">
+        <v>311</v>
+      </c>
+      <c r="N14" t="s">
+        <v>312</v>
+      </c>
+      <c r="O14" t="s">
+        <v>206</v>
+      </c>
+      <c r="P14" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>313</v>
+      </c>
+      <c r="R14" t="s">
+        <v>314</v>
+      </c>
+      <c r="S14" t="s">
+        <v>315</v>
+      </c>
+      <c r="T14" t="s">
+        <v>97</v>
+      </c>
+      <c r="U14" t="s">
+        <v>316</v>
+      </c>
+      <c r="V14" t="s">
+        <v>317</v>
+      </c>
+      <c r="W14" t="s">
+        <v>318</v>
+      </c>
+      <c r="X14" t="s">
+        <v>319</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>320</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>321</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>322</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>302</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s">
+        <v>324</v>
+      </c>
+      <c r="E15" t="s">
+        <v>325</v>
+      </c>
+      <c r="F15" t="s">
+        <v>326</v>
+      </c>
+      <c r="G15" t="s">
+        <v>327</v>
+      </c>
+      <c r="H15" t="s">
+        <v>328</v>
+      </c>
+      <c r="I15" t="s">
+        <v>329</v>
+      </c>
+      <c r="J15" t="s">
+        <v>90</v>
+      </c>
+      <c r="K15" t="s">
+        <v>66</v>
+      </c>
+      <c r="L15" t="s">
+        <v>330</v>
+      </c>
+      <c r="M15" t="s">
+        <v>331</v>
+      </c>
+      <c r="N15" t="s">
+        <v>332</v>
+      </c>
+      <c r="O15" t="s">
+        <v>44</v>
+      </c>
+      <c r="P15" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>333</v>
+      </c>
+      <c r="R15" t="s">
+        <v>334</v>
+      </c>
+      <c r="S15" t="s">
+        <v>335</v>
+      </c>
+      <c r="T15" t="s">
+        <v>336</v>
+      </c>
+      <c r="U15" t="s">
+        <v>337</v>
+      </c>
+      <c r="V15" t="s">
+        <v>338</v>
+      </c>
+      <c r="W15" t="s">
+        <v>339</v>
+      </c>
+      <c r="X15" t="s">
+        <v>340</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>342</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>343</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>302</v>
+      </c>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" t="s">
+        <v>345</v>
+      </c>
+      <c r="E16" t="s">
+        <v>346</v>
+      </c>
+      <c r="F16" t="s">
+        <v>347</v>
+      </c>
+      <c r="G16" t="s">
+        <v>348</v>
+      </c>
+      <c r="H16" t="s">
+        <v>349</v>
+      </c>
+      <c r="I16" t="s">
+        <v>350</v>
+      </c>
+      <c r="J16" t="s">
+        <v>90</v>
+      </c>
+      <c r="K16" t="s">
+        <v>181</v>
+      </c>
+      <c r="L16" t="s">
+        <v>351</v>
+      </c>
+      <c r="M16" t="s">
+        <v>352</v>
+      </c>
+      <c r="N16" t="s">
+        <v>353</v>
+      </c>
+      <c r="O16" t="s">
+        <v>354</v>
+      </c>
+      <c r="P16" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>355</v>
+      </c>
+      <c r="R16" t="s">
+        <v>356</v>
+      </c>
+      <c r="S16" t="s">
+        <v>357</v>
+      </c>
+      <c r="T16" t="s">
+        <v>251</v>
+      </c>
+      <c r="U16" t="s">
+        <v>358</v>
+      </c>
+      <c r="V16" t="s">
+        <v>359</v>
+      </c>
+      <c r="W16" t="s">
+        <v>360</v>
+      </c>
+      <c r="X16" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>361</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>362</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>363</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>302</v>
+      </c>
+      <c r="B17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" t="s">
+        <v>152</v>
+      </c>
+      <c r="D17" t="s">
+        <v>365</v>
+      </c>
+      <c r="E17" t="s">
+        <v>366</v>
+      </c>
+      <c r="F17" t="s">
+        <v>367</v>
+      </c>
+      <c r="G17" t="s">
+        <v>368</v>
+      </c>
+      <c r="H17" t="s">
+        <v>369</v>
+      </c>
+      <c r="I17" t="s">
+        <v>370</v>
+      </c>
+      <c r="J17" t="s">
+        <v>112</v>
+      </c>
+      <c r="K17" t="s">
+        <v>371</v>
+      </c>
+      <c r="L17" t="s">
+        <v>372</v>
+      </c>
+      <c r="M17" t="s">
+        <v>373</v>
+      </c>
+      <c r="N17" t="s">
+        <v>374</v>
+      </c>
+      <c r="O17" t="s">
+        <v>44</v>
+      </c>
+      <c r="P17" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>375</v>
+      </c>
+      <c r="R17" t="s">
+        <v>376</v>
+      </c>
+      <c r="S17" t="s">
+        <v>377</v>
+      </c>
+      <c r="T17" t="s">
+        <v>49</v>
+      </c>
+      <c r="U17" t="s">
+        <v>378</v>
+      </c>
+      <c r="V17" t="s">
+        <v>379</v>
+      </c>
+      <c r="W17" t="s">
+        <v>380</v>
+      </c>
+      <c r="X17" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>192</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>381</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>382</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>384</v>
+      </c>
+      <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" t="s">
+        <v>385</v>
+      </c>
+      <c r="D18" t="s">
+        <v>386</v>
+      </c>
+      <c r="E18" t="s">
+        <v>387</v>
+      </c>
+      <c r="F18" t="s">
+        <v>388</v>
+      </c>
+      <c r="G18" t="s">
+        <v>389</v>
+      </c>
+      <c r="H18" t="s">
+        <v>390</v>
+      </c>
+      <c r="I18" t="s">
+        <v>391</v>
+      </c>
+      <c r="J18" t="s">
+        <v>112</v>
+      </c>
+      <c r="K18" t="s">
+        <v>244</v>
+      </c>
+      <c r="L18" t="s">
+        <v>392</v>
+      </c>
+      <c r="M18" t="s">
+        <v>393</v>
+      </c>
+      <c r="N18" t="s">
+        <v>394</v>
+      </c>
+      <c r="O18" t="s">
+        <v>44</v>
+      </c>
+      <c r="P18" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>395</v>
+      </c>
+      <c r="R18" t="s">
+        <v>396</v>
+      </c>
+      <c r="S18" t="s">
+        <v>397</v>
+      </c>
+      <c r="T18" t="s">
+        <v>97</v>
+      </c>
+      <c r="U18" t="s">
+        <v>398</v>
+      </c>
+      <c r="V18" t="s">
+        <v>399</v>
+      </c>
+      <c r="W18" t="s">
+        <v>400</v>
+      </c>
+      <c r="X18" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>401</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>402</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>403</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>384</v>
+      </c>
+      <c r="B19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" t="s">
+        <v>385</v>
+      </c>
+      <c r="D19" t="s">
+        <v>405</v>
+      </c>
+      <c r="E19" t="s">
+        <v>406</v>
+      </c>
+      <c r="F19" t="s">
+        <v>407</v>
+      </c>
+      <c r="G19" t="s">
+        <v>408</v>
+      </c>
+      <c r="H19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I19" t="s">
+        <v>410</v>
+      </c>
+      <c r="J19" t="s">
+        <v>112</v>
+      </c>
+      <c r="K19" t="s">
+        <v>159</v>
+      </c>
+      <c r="L19" t="s">
+        <v>411</v>
+      </c>
+      <c r="M19" t="s">
+        <v>412</v>
+      </c>
+      <c r="N19" t="s">
+        <v>413</v>
+      </c>
+      <c r="O19" t="s">
+        <v>44</v>
+      </c>
+      <c r="P19" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>414</v>
+      </c>
+      <c r="R19" t="s">
+        <v>415</v>
+      </c>
+      <c r="S19" t="s">
+        <v>416</v>
+      </c>
+      <c r="T19" t="s">
+        <v>336</v>
+      </c>
+      <c r="U19" t="s">
+        <v>417</v>
+      </c>
+      <c r="V19" t="s">
+        <v>418</v>
+      </c>
+      <c r="W19" t="s">
+        <v>419</v>
+      </c>
+      <c r="X19" t="s">
+        <v>191</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>420</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>421</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>382</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>384</v>
+      </c>
+      <c r="B20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" t="s">
+        <v>174</v>
+      </c>
+      <c r="D20" t="s">
+        <v>423</v>
+      </c>
+      <c r="E20" t="s">
+        <v>424</v>
+      </c>
+      <c r="F20" t="s">
+        <v>425</v>
+      </c>
+      <c r="G20" t="s">
+        <v>426</v>
+      </c>
+      <c r="H20" t="s">
+        <v>427</v>
+      </c>
+      <c r="I20" t="s">
+        <v>428</v>
+      </c>
+      <c r="J20" t="s">
+        <v>112</v>
+      </c>
+      <c r="K20" t="s">
+        <v>429</v>
+      </c>
+      <c r="L20" t="s">
+        <v>430</v>
+      </c>
+      <c r="M20" t="s">
+        <v>393</v>
+      </c>
+      <c r="N20" t="s">
+        <v>431</v>
+      </c>
+      <c r="O20" t="s">
+        <v>44</v>
+      </c>
+      <c r="P20" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>432</v>
+      </c>
+      <c r="R20" t="s">
+        <v>433</v>
+      </c>
+      <c r="S20" t="s">
+        <v>434</v>
+      </c>
+      <c r="T20" t="s">
+        <v>251</v>
+      </c>
+      <c r="U20" t="s">
+        <v>435</v>
+      </c>
+      <c r="V20" t="s">
+        <v>436</v>
+      </c>
+      <c r="W20" t="s">
+        <v>437</v>
+      </c>
+      <c r="X20" t="s">
+        <v>438</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>256</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>439</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>440</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>441</v>
       </c>
     </row>
   </sheetData>
